--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_17-04-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_17-04-2026.xlsx
@@ -513,17 +513,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.80</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£18.70</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£19.04</t>
+          <t>£19.42</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£24.12</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£26.52</t>
+          <t>Cloudflare Blocked</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£26.56</t>
+          <t>Cloudflare Blocked</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£30.14</t>
+          <t>£30.74</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£33.18</t>
+          <t>£33.84</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£32.65</t>
+          <t>£33.30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>£39.68</t>
+          <t>£40.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£48.81</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£50.49</t>
+          <t>£51.50</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£49.49</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
